--- a/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer fruta</t>
+          <t>Menores según la edad en meses en la que empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,69</t>
+          <t>4,6; 5,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,89</t>
+          <t>5,32; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,81</t>
+          <t>5,37; 6,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,63</t>
+          <t>4,72; 5,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 6,56</t>
+          <t>5,11; 6,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,0</t>
+          <t>4,8; 5,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 5,44</t>
+          <t>4,76; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,35</t>
+          <t>5,31; 6,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,07</t>
+          <t>5,18; 6,04</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,69</t>
+          <t>4,47; 5,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,29</t>
+          <t>4,81; 6,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,43</t>
+          <t>5,32; 6,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,27</t>
+          <t>4,95; 6,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,68</t>
+          <t>4,68; 5,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,08</t>
+          <t>5,39; 7,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,87</t>
+          <t>4,88; 5,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,76</t>
+          <t>4,9; 5,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,48</t>
+          <t>5,51; 6,53</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,76</t>
+          <t>5,18; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,9</t>
+          <t>4,85; 5,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,11</t>
+          <t>4,79; 8,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,97</t>
+          <t>4,65; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,15</t>
+          <t>5,14; 7,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,95</t>
+          <t>5,82; 7,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,62</t>
+          <t>5,09; 6,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 6,38</t>
+          <t>5,18; 6,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,54</t>
+          <t>5,46; 7,51</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,34</t>
+          <t>4,3; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,63</t>
+          <t>5,04; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,29</t>
+          <t>5,7; 7,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,43</t>
+          <t>4,55; 5,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,58</t>
+          <t>5,22; 6,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,85</t>
+          <t>4,83; 5,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,26</t>
+          <t>4,56; 5,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 5,89</t>
+          <t>5,23; 5,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,44</t>
+          <t>5,49; 6,42</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,26</t>
+          <t>4,39; 5,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,22</t>
+          <t>4,96; 6,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,49</t>
+          <t>5,46; 7,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1137,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,29</t>
+          <t>5,49; 7,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,55</t>
+          <t>5,5; 8,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,35</t>
+          <t>4,67; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,42</t>
+          <t>5,34; 6,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,61</t>
+          <t>5,73; 7,71</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,82</t>
+          <t>4,91; 5,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 16,08</t>
+          <t>5,87; 15,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,52</t>
+          <t>4,33; 5,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 7,8</t>
+          <t>5,41; 7,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,57</t>
+          <t>4,63; 5,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,56</t>
+          <t>4,56; 5,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,79</t>
+          <t>5,32; 6,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,91</t>
+          <t>5,45; 11,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,4</t>
+          <t>4,55; 5,34</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,38</t>
+          <t>4,85; 5,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,53</t>
+          <t>5,41; 6,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,4</t>
+          <t>5,63; 6,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 5,64</t>
+          <t>5,06; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,02</t>
+          <t>5,41; 6,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,15</t>
+          <t>5,44; 6,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,4</t>
+          <t>5,02; 5,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,1</t>
+          <t>5,48; 6,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,15</t>
+          <t>5,62; 6,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,8</t>
+          <t>4,61; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,82</t>
+          <t>5,33; 6,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,65</t>
+          <t>5,35; 6,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 5,58</t>
+          <t>4,75; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,56</t>
+          <t>5,11; 6,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,96</t>
+          <t>4,79; 5,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,33</t>
+          <t>5,34; 6,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 6,04</t>
+          <t>5,21; 6,07</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,72</t>
+          <t>4,47; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,27</t>
+          <t>4,86; 6,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,38</t>
+          <t>5,35; 6,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,23</t>
+          <t>4,96; 6,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,78</t>
+          <t>4,71; 5,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,06</t>
+          <t>5,43; 6,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,82</t>
+          <t>4,89; 5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,71</t>
+          <t>4,88; 5,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,53</t>
+          <t>5,52; 6,44</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,7</t>
+          <t>5,18; 7,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,91</t>
+          <t>4,88; 5,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,41</t>
+          <t>4,81; 8,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,03</t>
+          <t>4,65; 6,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,03</t>
+          <t>5,16; 7,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,91</t>
+          <t>5,86; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,63</t>
+          <t>5,09; 6,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 6,35</t>
+          <t>5,17; 6,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,51</t>
+          <t>5,5; 7,55</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 5,64</t>
+          <t>5,06; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,22</t>
+          <t>5,7; 7,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,45</t>
+          <t>4,55; 5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,48</t>
+          <t>5,25; 6,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,83</t>
+          <t>4,9; 5,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,24</t>
+          <t>4,56; 5,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 5,89</t>
+          <t>5,22; 5,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,42</t>
+          <t>5,48; 6,48</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,23</t>
+          <t>4,37; 5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,27</t>
+          <t>4,96; 6,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 5,72</t>
+          <t>4,7; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,33</t>
+          <t>5,46; 7,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,83</t>
+          <t>5,53; 8,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,33</t>
+          <t>4,66; 5,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,37</t>
+          <t>5,32; 6,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,71</t>
+          <t>5,71; 7,7</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,83</t>
+          <t>4,84; 5,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 15,72</t>
+          <t>5,84; 15,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,48</t>
+          <t>4,31; 5,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 7,85</t>
+          <t>5,43; 7,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 5,56</t>
+          <t>4,59; 5,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,58</t>
+          <t>4,57; 5,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,78</t>
+          <t>5,33; 6,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,45</t>
+          <t>5,44; 11,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,34</t>
+          <t>4,56; 5,38</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,4</t>
+          <t>4,84; 5,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 6,51</t>
+          <t>5,42; 6,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,37</t>
+          <t>5,63; 6,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,62</t>
+          <t>5,07; 5,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 6,04</t>
+          <t>5,38; 6,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,14</t>
+          <t>5,45; 6,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,38</t>
+          <t>5,02; 5,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,11</t>
+          <t>5,49; 6,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,14</t>
+          <t>5,64; 6,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,06</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,85</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4,73; 5,63</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5,1; 6,56</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4,82; 6,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>4,61; 5,69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,33; 6,94</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,35; 6,74</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,75; 5,65</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,52</t>
+          <t>5,33; 6,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,91</t>
+          <t>5,4; 6,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 5,45</t>
+          <t>4,76; 5,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,36</t>
+          <t>5,3; 6,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,07</t>
+          <t>5,22; 6,07</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,01</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,48</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,98</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,75</t>
+          <t>4,95; 6,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,33</t>
+          <t>4,68; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,43</t>
+          <t>5,37; 7,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,27</t>
+          <t>4,47; 5,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,71</t>
+          <t>4,84; 6,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,93</t>
+          <t>5,32; 6,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,87</t>
+          <t>4,87; 5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,69</t>
+          <t>4,88; 5,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,44</t>
+          <t>5,5; 6,48</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,66</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,34</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,59</t>
+          <t>4,58; 6,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,96</t>
+          <t>5,13; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,43</t>
+          <t>5,71; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,97</t>
+          <t>5,17; 7,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,33</t>
+          <t>4,9; 5,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,23</t>
+          <t>4,71; 8,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,66</t>
+          <t>5,12; 6,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,28</t>
+          <t>5,18; 6,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,55</t>
+          <t>5,53; 7,54</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,86</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,33</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,33</t>
+          <t>4,56; 5,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,64</t>
+          <t>5,25; 6,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,29</t>
+          <t>4,88; 5,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,43</t>
+          <t>4,28; 5,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,57</t>
+          <t>5,03; 5,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,87</t>
+          <t>5,75; 7,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,21</t>
+          <t>4,57; 5,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 5,89</t>
+          <t>5,24; 5,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,48</t>
+          <t>5,49; 6,44</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,43</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,18</t>
+          <t>4,69; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,22</t>
+          <t>5,49; 7,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,75</t>
+          <t>5,51; 8,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,7</t>
+          <t>4,39; 5,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,28</t>
+          <t>4,98; 6,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,53</t>
+          <t>5,42; 7,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 5,35</t>
+          <t>4,68; 5,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,49</t>
+          <t>5,36; 6,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,7</t>
+          <t>5,65; 7,61</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,05</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,02</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,93</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,05</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,82</t>
+          <t>5,36; 7,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 15,92</t>
+          <t>4,61; 5,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,49</t>
+          <t>4,57; 5,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,86</t>
+          <t>4,9; 5,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,56</t>
+          <t>5,9; 16,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,55</t>
+          <t>4,29; 5,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,88</t>
+          <t>5,31; 6,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,21</t>
+          <t>5,4; 11,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,38</t>
+          <t>4,54; 5,4</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,76</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,73</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,68</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,39</t>
+          <t>5,05; 5,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,45</t>
+          <t>5,42; 6,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,34</t>
+          <t>5,45; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 5,59</t>
+          <t>4,85; 5,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,02</t>
+          <t>5,42; 6,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,19</t>
+          <t>5,64; 6,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,41</t>
+          <t>5,03; 5,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,11</t>
+          <t>5,48; 6,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,14</t>
+          <t>5,62; 6,15</t>
         </is>
       </c>
     </row>
